--- a/Primer ejercicio A asterisco.xlsx
+++ b/Primer ejercicio A asterisco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richa\Downloads\SEMESTRE-8\TOPICOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\richa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15D58DA7-F70C-4011-8AFE-01271CB067A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D13C387-AA7C-4695-A7A0-3EA94A3F565B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A975D930-4306-482C-8494-748E5BFC296C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A975D930-4306-482C-8494-748E5BFC296C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Inicio</t>
   </si>
@@ -96,7 +93,28 @@
     <t>G58 H50 F108 33</t>
   </si>
   <si>
-    <t>16,17,12,22,11,21,7,27,3</t>
+    <t>G68 H40 F108 4</t>
+  </si>
+  <si>
+    <t>G82 H20 F102 10</t>
+  </si>
+  <si>
+    <t>G96 H20 F116 14</t>
+  </si>
+  <si>
+    <t>G92 H10 F102 15</t>
+  </si>
+  <si>
+    <t>G92 H30 F122 9</t>
+  </si>
+  <si>
+    <t>G92 H30 F122 5</t>
+  </si>
+  <si>
+    <t>G106 H10 F116 19</t>
+  </si>
+  <si>
+    <t>G102 H0 F102 20</t>
   </si>
   <si>
     <r>
@@ -265,21 +283,249 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>,31,32,33,4,9</t>
-    </r>
-  </si>
-  <si>
-    <t>G68 H40 F108 4</t>
-  </si>
-  <si>
-    <t>G72 H30 F102 9</t>
+      <t>,31,32,33,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,9,5,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,14,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,19,</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,17,12,22,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,21,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,27,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,6 +551,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -365,16 +619,10 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -384,6 +632,12 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -701,77 +955,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A8AC91-370C-44A0-8067-6029C1F1DC3D}">
   <dimension ref="A2:N8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="2">
-        <v>5</v>
+      <c r="F4" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="3">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>16</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>18</v>
       </c>
-      <c r="E5" s="2">
-        <v>19</v>
-      </c>
-      <c r="F5" s="4">
-        <v>20</v>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="G5" t="s">
         <v>1</v>
@@ -779,72 +1033,72 @@
       <c r="I5" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="J5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
     </row>
-    <row r="6" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>23</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>24</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>25</v>
       </c>
       <c r="I6" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="J6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>28</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>29</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>34</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="1">
         <v>35</v>
       </c>
     </row>
